--- a/ig/nr-changes/StructureDefinition-as-mailbox-mss-metadata.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-mailbox-mss-metadata.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="173">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T15:25:16+00:00</t>
+    <t>2023-05-03T15:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,79 +326,6 @@
   </si>
   <si>
     <t>type</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.id</t>
-  </si>
-  <si>
-    <t>Extension.extension.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.url</t>
-  </si>
-  <si>
-    <t>Extension.extension.url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>Extension.extension:type.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
   </si>
   <si>
     <t>Valeurs possibles :
@@ -407,6 +334,79 @@
 PER pour une BAL personnelle, rattachée à une personne physique</t>
   </si>
   <si>
+    <t>Extension.extension:type.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -443,6 +443,9 @@
     <t>responsible</t>
   </si>
   <si>
+    <t>Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
+  </si>
+  <si>
     <t>Extension.extension:responsible.id</t>
   </si>
   <si>
@@ -455,15 +458,15 @@
     <t>Extension.extension:responsible.value[x]</t>
   </si>
   <si>
-    <t>Texte libre donnant les coordonnées de la (ou des) personne(s) responsable(s) au niveau opérationnel de la boîte aux lettres. Non renseigné pour les types de boîte aux lettres "PER".</t>
-  </si>
-  <si>
     <t>Extension.extension:service</t>
   </si>
   <si>
     <t>service</t>
   </si>
   <si>
+    <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
+  </si>
+  <si>
     <t>Extension.extension:service.id</t>
   </si>
   <si>
@@ -476,21 +479,15 @@
     <t>Extension.extension:service.value[x]</t>
   </si>
   <si>
-    <t>Extension.extension:service.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t>Nom et description du service de rattachement de l’utilisateur de la boîte aux lettres dans l’organisation.</t>
-  </si>
-  <si>
     <t>Extension.extension:phone</t>
   </si>
   <si>
     <t>phone</t>
   </si>
   <si>
+    <t>Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté</t>
+  </si>
+  <si>
     <t>Extension.extension:phone.id</t>
   </si>
   <si>
@@ -503,16 +500,14 @@
     <t>Extension.extension:phone.value[x]</t>
   </si>
   <si>
-    <t>Extension.extension:phone.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>Coordonnées téléphoniques spécifiques à l’usage de la boîte aux lettres MSSanté</t>
-  </si>
-  <si>
     <t>Extension.extension:digitization</t>
   </si>
   <si>
     <t>digitization</t>
+  </si>
+  <si>
+    <t>Indicateur d’acceptation de la dématérialisation (ou « Zéro papier »). - O : Dématérialisation acceptée 
+- N : Dématérialisation refusée</t>
   </si>
   <si>
     <t>Extension.extension:digitization.id</t>
@@ -531,25 +526,16 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:digitization.value[x]:valueBoolean</t>
-  </si>
-  <si>
-    <t>valueBoolean</t>
-  </si>
-  <si>
-    <t>Indicateur d’acceptation de la dématérialisation (ou « Zéro papier »</t>
-  </si>
-  <si>
-    <t>- O : Dématérialisation acceptée 
-- N : Dématérialisation refusée</t>
-  </si>
-  <si>
     <t>Extension.extension:publication</t>
   </si>
   <si>
     <t>publication</t>
   </si>
   <si>
+    <t>Indicateur liste rouge. O: Boîte aux lettres en liste rouge;
+N: La boîte aux lettres peut être publiée</t>
+  </si>
+  <si>
     <t>Extension.extension:publication.id</t>
   </si>
   <si>
@@ -560,16 +546,6 @@
   </si>
   <si>
     <t>Extension.extension:publication.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:publication.value[x]:valueBoolean</t>
-  </si>
-  <si>
-    <t>ndicateur liste rouge</t>
-  </si>
-  <si>
-    <t>O: Boîte aux lettres en liste rouge;
-N: La boîte aux lettres peut être publiée</t>
   </si>
   <si>
     <t>base64Binary
@@ -891,7 +867,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK46"/>
+  <dimension ref="A1:AK42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="54.2421875" customWidth="true" bestFit="true"/>
@@ -1598,7 +1574,7 @@
         <v>28</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1669,10 +1645,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1695,16 +1671,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1754,7 +1730,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>82</v>
@@ -1774,10 +1750,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1800,13 +1776,13 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1845,17 +1821,17 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1867,7 +1843,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>99</v>
@@ -1875,13 +1851,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -1903,13 +1879,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1960,7 +1936,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -1972,7 +1948,7 @@
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>99</v>
@@ -2014,7 +1990,7 @@
         <v>28</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2220,7 +2196,7 @@
         <v>28</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2294,7 +2270,7 @@
         <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2317,16 +2293,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2376,7 +2352,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>82</v>
@@ -2399,7 +2375,7 @@
         <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2428,7 +2404,7 @@
         <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2479,7 +2455,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2491,7 +2467,7 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>99</v>
@@ -2530,10 +2506,10 @@
         <v>90</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2604,7 +2580,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>104</v>
@@ -2707,7 +2683,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
         <v>106</v>
@@ -2739,7 +2715,7 @@
         <v>28</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2810,10 +2786,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2836,16 +2812,16 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2895,7 +2871,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -2915,10 +2891,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2944,10 +2920,10 @@
         <v>83</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2998,7 +2974,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3010,7 +2986,7 @@
         <v>80</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>99</v>
@@ -3049,10 +3025,10 @@
         <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3123,7 +3099,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>104</v>
@@ -3226,7 +3202,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>106</v>
@@ -3258,7 +3234,7 @@
         <v>28</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3329,10 +3305,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3355,16 +3331,16 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3414,7 +3390,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -3434,10 +3410,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3463,10 +3439,10 @@
         <v>83</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3505,17 +3481,19 @@
         <v>76</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3527,7 +3505,7 @@
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>99</v>
@@ -3535,13 +3513,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>76</v>
@@ -3563,13 +3541,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3620,34 +3598,32 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>76</v>
       </c>
@@ -3668,13 +3644,13 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3725,22 +3701,22 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28">
@@ -3748,7 +3724,7 @@
         <v>154</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3759,7 +3735,7 @@
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -3771,13 +3747,13 @@
         <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3816,34 +3792,34 @@
         <v>76</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
@@ -3851,7 +3827,7 @@
         <v>155</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3859,10 +3835,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -3874,22 +3850,24 @@
         <v>76</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>76</v>
@@ -3919,34 +3897,34 @@
         <v>76</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
@@ -3954,7 +3932,7 @@
         <v>156</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3962,7 +3940,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>82</v>
@@ -3977,24 +3955,22 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>76</v>
@@ -4036,19 +4012,19 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>99</v>
@@ -4059,9 +4035,11 @@
         <v>157</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>76</v>
       </c>
@@ -4082,13 +4060,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4127,44 +4105,44 @@
         <v>76</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>76</v>
       </c>
@@ -4188,10 +4166,10 @@
         <v>83</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4242,7 +4220,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4251,25 +4229,23 @@
         <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>76</v>
       </c>
@@ -4278,7 +4254,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>76</v>
@@ -4296,7 +4272,7 @@
         <v>28</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4335,16 +4311,16 @@
         <v>76</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>97</v>
@@ -4370,7 +4346,7 @@
         <v>162</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4378,7 +4354,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>82</v>
@@ -4393,22 +4369,24 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>76</v>
@@ -4450,10 +4428,10 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>82</v>
@@ -4465,7 +4443,7 @@
         <v>76</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
@@ -4473,7 +4451,7 @@
         <v>163</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4484,7 +4462,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -4496,13 +4474,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4541,50 +4519,52 @@
         <v>76</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>82</v>
@@ -4599,24 +4579,22 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>76</v>
@@ -4658,30 +4636,30 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4704,13 +4682,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>83</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4749,17 +4727,19 @@
         <v>76</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -4768,25 +4748,23 @@
         <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>76</v>
       </c>
@@ -4795,7 +4773,7 @@
         <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>76</v>
@@ -4807,17 +4785,15 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>169</v>
+        <v>28</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -4854,52 +4830,50 @@
         <v>76</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>82</v>
@@ -4914,22 +4888,24 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>76</v>
@@ -4971,30 +4947,30 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5017,13 +4993,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5074,7 +5050,7 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -5083,21 +5059,21 @@
         <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5105,10 +5081,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
@@ -5120,22 +5096,24 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>76</v>
@@ -5165,42 +5143,42 @@
         <v>76</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5208,10 +5186,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>76</v>
@@ -5223,24 +5201,22 @@
         <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>172</v>
+        <v>76</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>76</v>
@@ -5282,437 +5258,21 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AC43" s="2"/>
-      <c r="AD43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK46" t="s" s="2">
         <v>99</v>
       </c>
     </row>

--- a/ig/nr-changes/StructureDefinition-as-mailbox-mss-metadata.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T15:57:05+00:00</t>
+    <t>2023-05-03T16:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-changes/StructureDefinition-as-mailbox-mss-metadata.xlsx
+++ b/ig/nr-changes/StructureDefinition-as-mailbox-mss-metadata.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T16:01:19+00:00</t>
+    <t>2023-05-03T16:12:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
